--- a/formatos/FORMATO NO ADEUDO PARA TOOL ID.xlsx
+++ b/formatos/FORMATO NO ADEUDO PARA TOOL ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frida.arroyo\Documents\Documentos sofia y QDOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E620CF6-A5A6-4E84-9D61-2595FD80B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4129CCF-9FD0-4C45-88FE-25E0E2D474EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2925" windowWidth="29040" windowHeight="15720" xr2:uid="{9FD6B040-32E7-4B8A-9884-21ED8CE8A50E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9FD6B040-32E7-4B8A-9884-21ED8CE8A50E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>CONSTANCIA DE NO ADEUDO</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>FIRMA COLABORADOR:______________________________________</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>VIDA UTIL</t>
   </si>
 </sst>
 </file>
@@ -171,7 +177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -287,11 +293,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -313,17 +343,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -371,6 +394,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -405,9 +434,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>654050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>62757</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -437,7 +466,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="19051" y="28574"/>
-          <a:ext cx="1549399" cy="790575"/>
+          <a:ext cx="1543049" cy="656483"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -927,7 +956,7 @@
     <col min="2" max="2" width="10.26953125" customWidth="1"/>
     <col min="3" max="3" width="56.54296875" customWidth="1"/>
     <col min="4" max="4" width="17.7265625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
     <col min="7" max="7" width="9.81640625" customWidth="1"/>
     <col min="8" max="8" width="11.453125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
@@ -938,31 +967,31 @@
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="22"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H2" s="19"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="6"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="21" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="16"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
@@ -976,10 +1005,10 @@
       <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
@@ -987,8 +1016,8 @@
         <v>5</v>
       </c>
       <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="5"/>
     </row>
@@ -1006,28 +1035,28 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="13"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="5"/>
     </row>
@@ -1052,11 +1081,17 @@
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="34" t="s">
         <v>10</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>17</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -1066,6 +1101,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1074,6 +1111,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
       <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -1082,6 +1121,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -1090,6 +1131,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -1098,6 +1141,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -1106,6 +1151,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -1114,6 +1161,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
@@ -1122,6 +1171,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
@@ -1129,6 +1180,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
@@ -1136,6 +1189,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
@@ -1147,76 +1202,76 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="29"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="29"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="29"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -1231,10 +1286,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="23"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -1253,9 +1308,9 @@
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C2:D3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B22:F29"/>
+    <mergeCell ref="C2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
